--- a/conformance/fixtures/097-native-formula-static-cell-preserved/expected.xlsx
+++ b/conformance/fixtures/097-native-formula-static-cell-preserved/expected.xlsx
@@ -421,13 +421,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B4" t="str">
+        <f>LOWER(A4)</f>
+        <v>footer</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
-      </c>
-      <c r="B5" t="str">
-        <f>LOWER(A4)</f>
-        <v>footer</v>
       </c>
     </row>
   </sheetData>
